--- a/Results/Sit_To_Stand/Comparisons/Overall_Comparison_Sit_To_Stand.xlsx
+++ b/Results/Sit_To_Stand/Comparisons/Overall_Comparison_Sit_To_Stand.xlsx
@@ -10,6 +10,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All_Scenarios" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Deltas_vs_Baseline" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Base_vs_Pipeline_PCA" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Base_vs_Detected_Action" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Base_vs_Detected_Action_Pipelin" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -742,6 +744,258 @@
       </c>
       <c r="L7" t="n">
         <v>11.48910630174551</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Detected_Action</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Random Forest</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>72.26666666666667</v>
+      </c>
+      <c r="D8" t="n">
+        <v>8.751719407784542</v>
+      </c>
+      <c r="E8" t="n">
+        <v>74.83650793650794</v>
+      </c>
+      <c r="F8" t="n">
+        <v>9.20868881054591</v>
+      </c>
+      <c r="G8" t="n">
+        <v>72.26666666666667</v>
+      </c>
+      <c r="H8" t="n">
+        <v>8.751719407784543</v>
+      </c>
+      <c r="I8" t="n">
+        <v>86.13333333333334</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4.375859703892267</v>
+      </c>
+      <c r="K8" t="n">
+        <v>71.44403004403004</v>
+      </c>
+      <c r="L8" t="n">
+        <v>8.871430794514362</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Detected_Action</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>65.06666666666666</v>
+      </c>
+      <c r="D9" t="n">
+        <v>10.59000227328343</v>
+      </c>
+      <c r="E9" t="n">
+        <v>67.60952380952381</v>
+      </c>
+      <c r="F9" t="n">
+        <v>11.11502914984372</v>
+      </c>
+      <c r="G9" t="n">
+        <v>65.06666666666666</v>
+      </c>
+      <c r="H9" t="n">
+        <v>10.59000227328343</v>
+      </c>
+      <c r="I9" t="n">
+        <v>82.53333333333335</v>
+      </c>
+      <c r="J9" t="n">
+        <v>5.295001136641714</v>
+      </c>
+      <c r="K9" t="n">
+        <v>63.35574055574057</v>
+      </c>
+      <c r="L9" t="n">
+        <v>11.26754419651733</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Detected_Action</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>61.86666666666666</v>
+      </c>
+      <c r="D10" t="n">
+        <v>13.67885635245546</v>
+      </c>
+      <c r="E10" t="n">
+        <v>62.9068783068783</v>
+      </c>
+      <c r="F10" t="n">
+        <v>15.52316226083301</v>
+      </c>
+      <c r="G10" t="n">
+        <v>61.86666666666667</v>
+      </c>
+      <c r="H10" t="n">
+        <v>13.67885635245546</v>
+      </c>
+      <c r="I10" t="n">
+        <v>80.93333333333334</v>
+      </c>
+      <c r="J10" t="n">
+        <v>6.839428176227732</v>
+      </c>
+      <c r="K10" t="n">
+        <v>59.11518851518851</v>
+      </c>
+      <c r="L10" t="n">
+        <v>14.53411180369726</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Detected_Action_Pipeline_PCA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Random Forest</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>68</v>
+      </c>
+      <c r="D11" t="n">
+        <v>11.70628194761415</v>
+      </c>
+      <c r="E11" t="n">
+        <v>71.58273208273208</v>
+      </c>
+      <c r="F11" t="n">
+        <v>11.5775463662813</v>
+      </c>
+      <c r="G11" t="n">
+        <v>68</v>
+      </c>
+      <c r="H11" t="n">
+        <v>11.70628194761416</v>
+      </c>
+      <c r="I11" t="n">
+        <v>84</v>
+      </c>
+      <c r="J11" t="n">
+        <v>5.853140973807077</v>
+      </c>
+      <c r="K11" t="n">
+        <v>67.1992081992082</v>
+      </c>
+      <c r="L11" t="n">
+        <v>11.93692708826609</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Detected_Action_Pipeline_PCA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>67.99999999999999</v>
+      </c>
+      <c r="D12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" t="n">
+        <v>69.32698412698413</v>
+      </c>
+      <c r="F12" t="n">
+        <v>10.60318326640016</v>
+      </c>
+      <c r="G12" t="n">
+        <v>68</v>
+      </c>
+      <c r="H12" t="n">
+        <v>10</v>
+      </c>
+      <c r="I12" t="n">
+        <v>84</v>
+      </c>
+      <c r="J12" t="n">
+        <v>5.000000000000003</v>
+      </c>
+      <c r="K12" t="n">
+        <v>66.5882413882414</v>
+      </c>
+      <c r="L12" t="n">
+        <v>10.30111500169794</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Detected_Action_Pipeline_PCA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>61.06666666666667</v>
+      </c>
+      <c r="D13" t="n">
+        <v>13.2888145668676</v>
+      </c>
+      <c r="E13" t="n">
+        <v>61.67301587301586</v>
+      </c>
+      <c r="F13" t="n">
+        <v>17.47332222721096</v>
+      </c>
+      <c r="G13" t="n">
+        <v>61.06666666666667</v>
+      </c>
+      <c r="H13" t="n">
+        <v>13.2888145668676</v>
+      </c>
+      <c r="I13" t="n">
+        <v>80.53333333333333</v>
+      </c>
+      <c r="J13" t="n">
+        <v>6.644407283433802</v>
+      </c>
+      <c r="K13" t="n">
+        <v>57.66668886668887</v>
+      </c>
+      <c r="L13" t="n">
+        <v>14.4965664916627</v>
       </c>
     </row>
   </sheetData>
@@ -755,7 +1009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q4"/>
+  <dimension ref="A1:Q10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1014,6 +1268,348 @@
       </c>
       <c r="Q4" t="n">
         <v>-0.6313686313686233</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Detected_Action</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Random Forest</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>72.26666666666667</v>
+      </c>
+      <c r="D5" t="n">
+        <v>74.83650793650794</v>
+      </c>
+      <c r="E5" t="n">
+        <v>72.26666666666667</v>
+      </c>
+      <c r="F5" t="n">
+        <v>86.13333333333334</v>
+      </c>
+      <c r="G5" t="n">
+        <v>71.44403004403004</v>
+      </c>
+      <c r="H5" t="n">
+        <v>82.13333333333334</v>
+      </c>
+      <c r="I5" t="n">
+        <v>84.56825396825397</v>
+      </c>
+      <c r="J5" t="n">
+        <v>82.13333333333334</v>
+      </c>
+      <c r="K5" t="n">
+        <v>91.06666666666666</v>
+      </c>
+      <c r="L5" t="n">
+        <v>81.60462500462501</v>
+      </c>
+      <c r="M5" t="n">
+        <v>-9.866666666666674</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-9.731746031746027</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-9.866666666666674</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-4.933333333333323</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-10.16059496059496</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Detected_Action</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>65.06666666666666</v>
+      </c>
+      <c r="D6" t="n">
+        <v>67.60952380952381</v>
+      </c>
+      <c r="E6" t="n">
+        <v>65.06666666666666</v>
+      </c>
+      <c r="F6" t="n">
+        <v>82.53333333333335</v>
+      </c>
+      <c r="G6" t="n">
+        <v>63.35574055574057</v>
+      </c>
+      <c r="H6" t="n">
+        <v>76.26666666666667</v>
+      </c>
+      <c r="I6" t="n">
+        <v>80.86455026455027</v>
+      </c>
+      <c r="J6" t="n">
+        <v>76.26666666666667</v>
+      </c>
+      <c r="K6" t="n">
+        <v>88.13333333333334</v>
+      </c>
+      <c r="L6" t="n">
+        <v>75.31530125647772</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-11.2</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-13.25502645502647</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-11.2</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-5.599999999999994</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-11.95956070073716</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Detected_Action</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>61.86666666666666</v>
+      </c>
+      <c r="D7" t="n">
+        <v>62.9068783068783</v>
+      </c>
+      <c r="E7" t="n">
+        <v>61.86666666666667</v>
+      </c>
+      <c r="F7" t="n">
+        <v>80.93333333333334</v>
+      </c>
+      <c r="G7" t="n">
+        <v>59.11518851518851</v>
+      </c>
+      <c r="H7" t="n">
+        <v>66.13333333333333</v>
+      </c>
+      <c r="I7" t="n">
+        <v>67.02063492063492</v>
+      </c>
+      <c r="J7" t="n">
+        <v>66.13333333333333</v>
+      </c>
+      <c r="K7" t="n">
+        <v>83.06666666666668</v>
+      </c>
+      <c r="L7" t="n">
+        <v>63.603626003626</v>
+      </c>
+      <c r="M7" t="n">
+        <v>-4.266666666666666</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-4.113756613756614</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-4.266666666666659</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-2.13333333333334</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-4.488437488437484</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Detected_Action_Pipeline_PCA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Random Forest</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>68</v>
+      </c>
+      <c r="D8" t="n">
+        <v>71.58273208273208</v>
+      </c>
+      <c r="E8" t="n">
+        <v>68</v>
+      </c>
+      <c r="F8" t="n">
+        <v>84</v>
+      </c>
+      <c r="G8" t="n">
+        <v>67.1992081992082</v>
+      </c>
+      <c r="H8" t="n">
+        <v>82.13333333333334</v>
+      </c>
+      <c r="I8" t="n">
+        <v>84.56825396825397</v>
+      </c>
+      <c r="J8" t="n">
+        <v>82.13333333333334</v>
+      </c>
+      <c r="K8" t="n">
+        <v>91.06666666666666</v>
+      </c>
+      <c r="L8" t="n">
+        <v>81.60462500462501</v>
+      </c>
+      <c r="M8" t="n">
+        <v>-14.13333333333334</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-12.98552188552189</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-14.13333333333334</v>
+      </c>
+      <c r="P8" t="n">
+        <v>-7.066666666666663</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-14.40541680541681</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Detected_Action_Pipeline_PCA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>67.99999999999999</v>
+      </c>
+      <c r="D9" t="n">
+        <v>69.32698412698413</v>
+      </c>
+      <c r="E9" t="n">
+        <v>68</v>
+      </c>
+      <c r="F9" t="n">
+        <v>84</v>
+      </c>
+      <c r="G9" t="n">
+        <v>66.5882413882414</v>
+      </c>
+      <c r="H9" t="n">
+        <v>76.26666666666667</v>
+      </c>
+      <c r="I9" t="n">
+        <v>80.86455026455027</v>
+      </c>
+      <c r="J9" t="n">
+        <v>76.26666666666667</v>
+      </c>
+      <c r="K9" t="n">
+        <v>88.13333333333334</v>
+      </c>
+      <c r="L9" t="n">
+        <v>75.31530125647772</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-8.26666666666668</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-11.53756613756615</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-8.266666666666666</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-4.13333333333334</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-8.727059868236324</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Detected_Action_Pipeline_PCA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>61.06666666666667</v>
+      </c>
+      <c r="D10" t="n">
+        <v>61.67301587301586</v>
+      </c>
+      <c r="E10" t="n">
+        <v>61.06666666666667</v>
+      </c>
+      <c r="F10" t="n">
+        <v>80.53333333333333</v>
+      </c>
+      <c r="G10" t="n">
+        <v>57.66668886668887</v>
+      </c>
+      <c r="H10" t="n">
+        <v>66.13333333333333</v>
+      </c>
+      <c r="I10" t="n">
+        <v>67.02063492063492</v>
+      </c>
+      <c r="J10" t="n">
+        <v>66.13333333333333</v>
+      </c>
+      <c r="K10" t="n">
+        <v>83.06666666666668</v>
+      </c>
+      <c r="L10" t="n">
+        <v>63.603626003626</v>
+      </c>
+      <c r="M10" t="n">
+        <v>-5.066666666666656</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-5.347619047619055</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-5.066666666666656</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-2.533333333333346</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-5.936937136937132</v>
       </c>
     </row>
   </sheetData>
@@ -1103,4 +1699,172 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Detected_Action</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Accuracy_Difference</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>66.13333333333333</v>
+      </c>
+      <c r="C2" t="n">
+        <v>61.86666666666666</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-4.266666666666666</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>76.26666666666667</v>
+      </c>
+      <c r="C3" t="n">
+        <v>65.06666666666666</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-11.2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Random Forest</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>82.13333333333334</v>
+      </c>
+      <c r="C4" t="n">
+        <v>72.26666666666667</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-9.866666666666674</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Detected_Action_Pipeline_PCA</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Accuracy_Difference</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>66.13333333333333</v>
+      </c>
+      <c r="C2" t="n">
+        <v>61.06666666666667</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-5.066666666666656</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>76.26666666666667</v>
+      </c>
+      <c r="C3" t="n">
+        <v>67.99999999999999</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-8.26666666666668</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Random Forest</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>82.13333333333334</v>
+      </c>
+      <c r="C4" t="n">
+        <v>68</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-14.13333333333334</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>